--- a/Budget/data/budget_2025.xlsx
+++ b/Budget/data/budget_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF626D57-3341-421A-B6F3-FB9C32792EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FE5E27-D354-4590-9697-E76B5F0D4BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{653CFB00-AA5A-438D-94B2-54F13C89823F}"/>
   </bookViews>
@@ -520,11 +520,11 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,16 +548,16 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>6699829527</v>
-      </c>
-      <c r="C2" s="2">
-        <v>31475545895</v>
-      </c>
-      <c r="D2" s="2">
-        <v>38175375421</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="B2" s="3">
+        <v>6699829526.5200005</v>
+      </c>
+      <c r="C2" s="3">
+        <v>31475545894.93</v>
+      </c>
+      <c r="D2" s="3">
+        <v>38175375421.459999</v>
+      </c>
+      <c r="E2" s="3">
         <v>10664655500</v>
       </c>
       <c r="F2" s="3">
@@ -568,16 +568,16 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
-        <v>490472582.30000001</v>
-      </c>
-      <c r="C3" s="2">
-        <v>984312234.60000002</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1474784817</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="B3" s="3">
+        <v>490472582.25</v>
+      </c>
+      <c r="C3" s="3">
+        <v>984312234.59000003</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1474784816.8399999</v>
+      </c>
+      <c r="E3" s="3">
         <v>3019540000</v>
       </c>
       <c r="F3" s="3">
@@ -588,37 +588,37 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
-        <v>362861189.19999999</v>
-      </c>
-      <c r="C4" s="2">
-        <v>26812946.48</v>
-      </c>
-      <c r="D4" s="2">
-        <v>389674135.69999999</v>
-      </c>
-      <c r="E4" s="2">
-        <v>6225500000</v>
+      <c r="B4" s="3">
+        <v>23295299702.720001</v>
+      </c>
+      <c r="C4" s="3">
+        <v>20466144369.43</v>
+      </c>
+      <c r="D4" s="3">
+        <v>43761444072.160004</v>
+      </c>
+      <c r="E4" s="3">
+        <v>7664500000</v>
       </c>
       <c r="F4" s="3">
-        <v>6615174135.6800003</v>
+        <v>51425944072.160004</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>215899318.19999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>72949354.549999997</v>
       </c>
-      <c r="D5" s="2">
-        <v>288848672.80000001</v>
-      </c>
-      <c r="E5" s="2">
-        <v>271562000000</v>
+      <c r="D5" s="3">
+        <v>288848672.75</v>
+      </c>
+      <c r="E5" s="3">
+        <v>271562000000.10001</v>
       </c>
       <c r="F5" s="3">
         <v>271850848672.85001</v>
@@ -628,36 +628,36 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
-        <v>283088351.69999999</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="B6" s="3">
+        <v>283088351.72000003</v>
+      </c>
+      <c r="C6" s="3">
         <v>28107274.530000001</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>312191149.89999998</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>312191149.89999998</v>
+        <v>2849428941.04</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
-        <v>613367392.20000005</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B7" s="3">
+        <v>613367392.23000002</v>
+      </c>
+      <c r="C7" s="3">
         <v>20339716.079999998</v>
       </c>
-      <c r="D7" s="2">
-        <v>633707108.29999995</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="3">
+        <v>633707108.30999994</v>
+      </c>
+      <c r="E7" s="3">
         <v>3125000000</v>
       </c>
       <c r="F7" s="3">
@@ -668,17 +668,17 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
-        <v>120066559.5</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B8" s="3">
+        <v>120066559.48</v>
+      </c>
+      <c r="C8" s="3">
         <v>13384103.65</v>
       </c>
-      <c r="D8" s="2">
-        <v>133450663.09999999</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10411000000</v>
+      <c r="D8" s="3">
+        <v>133450663.13</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10411000000.049999</v>
       </c>
       <c r="F8" s="3">
         <v>10544450663.18</v>
@@ -688,16 +688,16 @@
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>112311864</v>
       </c>
-      <c r="C9" s="2">
-        <v>282383698.10000002</v>
-      </c>
-      <c r="D9" s="2">
-        <v>394695562.10000002</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="C9" s="3">
+        <v>282383698.13</v>
+      </c>
+      <c r="D9" s="3">
+        <v>394695562.13</v>
+      </c>
+      <c r="E9" s="3">
         <v>4569000000</v>
       </c>
       <c r="F9" s="3">
@@ -708,36 +708,36 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2">
-        <v>697308192.60000002</v>
+      <c r="B10" s="3">
+        <v>697308192.55999994</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="2">
-        <v>697308192.60000002</v>
+      <c r="D10" s="3">
+        <v>697308192.55999994</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>697308192.55999994</v>
+        <v>7971967646.4799995</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>508275684.10000002</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>57531730.079999998</v>
       </c>
-      <c r="D11" s="2">
-        <v>565807414.20000005</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11" s="3">
+        <v>565807414.17999995</v>
+      </c>
+      <c r="E11" s="3">
         <v>15336833333</v>
       </c>
       <c r="F11" s="3">
@@ -748,16 +748,16 @@
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>22572200</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>19227600</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>41799800</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>935000000</v>
       </c>
       <c r="F12" s="3">
@@ -768,16 +768,16 @@
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="2">
-        <v>1559128693</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3245100261</v>
-      </c>
-      <c r="D13" s="2">
-        <v>4804228954</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="B13" s="3">
+        <v>1559128693.4400001</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3245100260.8800001</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4804228954.3199997</v>
+      </c>
+      <c r="E13" s="3">
         <v>6058000000</v>
       </c>
       <c r="F13" s="3">
@@ -788,16 +788,16 @@
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>70113487.5</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>19910052.690000001</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>90023540.189999998</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <v>185000000</v>
       </c>
       <c r="F14" s="3">
@@ -808,16 +808,16 @@
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2">
-        <v>5983750263</v>
-      </c>
-      <c r="C15" s="2">
-        <v>342004375.89999998</v>
-      </c>
-      <c r="D15" s="2">
-        <v>6959461747</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="B15" s="3">
+        <v>5983750262.9399996</v>
+      </c>
+      <c r="C15" s="3">
+        <v>342004375.88</v>
+      </c>
+      <c r="D15" s="3">
+        <v>6959461747.1199999</v>
+      </c>
+      <c r="E15" s="3">
         <v>11299600000</v>
       </c>
       <c r="F15" s="3">
@@ -828,16 +828,16 @@
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>565015287.39999998</v>
       </c>
-      <c r="C16" s="2">
-        <v>109712371.7</v>
-      </c>
-      <c r="D16" s="2">
-        <v>674727659.10000002</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="C16" s="3">
+        <v>109712371.73999999</v>
+      </c>
+      <c r="D16" s="3">
+        <v>674727659.13999999</v>
+      </c>
+      <c r="E16" s="3">
         <v>699000000</v>
       </c>
       <c r="F16" s="3">
@@ -848,16 +848,16 @@
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>347591067.60000002</v>
       </c>
-      <c r="C17" s="2">
-        <v>788911484.5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1136502552</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="C17" s="3">
+        <v>788911484.51999998</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1136502552.1199999</v>
+      </c>
+      <c r="E17" s="3">
         <v>5460318000</v>
       </c>
       <c r="F17" s="3">
@@ -868,16 +868,16 @@
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2">
-        <v>1066410186</v>
-      </c>
-      <c r="C18" s="2">
-        <v>295920722.10000002</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1362330908</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="B18" s="3">
+        <v>1066410186.2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>295920722.08999997</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1362330908.29</v>
+      </c>
+      <c r="E18" s="3">
         <v>866000000</v>
       </c>
       <c r="F18" s="3">
@@ -888,14 +888,14 @@
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="2">
-        <v>221583990</v>
+      <c r="B19" s="3">
+        <v>221583990.03</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
       </c>
-      <c r="D19" s="2">
-        <v>221583990</v>
+      <c r="D19" s="3">
+        <v>221583990.03</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -908,13 +908,13 @@
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>7276500</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>7276500</v>
       </c>
       <c r="E20" s="2">
@@ -928,13 +928,13 @@
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>7210350</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>7210350</v>
       </c>
       <c r="E21" s="2">
@@ -948,16 +948,16 @@
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="2">
-        <v>135779993.09999999</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B22" s="3">
+        <v>135779993.05000001</v>
+      </c>
+      <c r="C22" s="3">
         <v>15107400</v>
       </c>
-      <c r="D22" s="2">
-        <v>150887393.09999999</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22" s="3">
+        <v>150887393.05000001</v>
+      </c>
+      <c r="E22" s="3">
         <v>2701500000</v>
       </c>
       <c r="F22" s="3">
@@ -968,16 +968,16 @@
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>114446652.8</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>9751322</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>124197974.8</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <v>2610600000</v>
       </c>
       <c r="F23" s="3">
@@ -988,17 +988,17 @@
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2">
-        <v>138600177.30000001</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="3">
+        <v>138600177.31999999</v>
+      </c>
+      <c r="C24" s="3">
         <v>30694000</v>
       </c>
-      <c r="D24" s="2">
-        <v>169294177.30000001</v>
-      </c>
-      <c r="E24" s="2">
-        <v>10609500000</v>
+      <c r="D24" s="3">
+        <v>169294177.31999999</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10609500000.02</v>
       </c>
       <c r="F24" s="3">
         <v>10778794177.34</v>
@@ -1008,16 +1008,16 @@
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>280883462.60000002</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>29209950</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>310093412.60000002</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="3">
         <v>547000000</v>
       </c>
       <c r="F25" s="3">
@@ -1028,17 +1028,17 @@
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>258086115.19999999</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>74436821.459999993</v>
       </c>
-      <c r="D26" s="2">
-        <v>332522936.69999999</v>
-      </c>
-      <c r="E26" s="2">
-        <v>4015000000</v>
+      <c r="D26" s="3">
+        <v>332522936.66000003</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4015000000.0999999</v>
       </c>
       <c r="F26" s="3">
         <v>4347522936.7600002</v>
@@ -1048,17 +1048,17 @@
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>576835303.79999995</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>43100895.200000003</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>619936199</v>
       </c>
-      <c r="E27" s="2">
-        <v>4109700000</v>
+      <c r="E27" s="3">
+        <v>4109700000.0999999</v>
       </c>
       <c r="F27" s="3">
         <v>4729636199.1000004</v>
@@ -1068,16 +1068,16 @@
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2">
-        <v>628826114.29999995</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="3">
+        <v>628826114.26999998</v>
+      </c>
+      <c r="C28" s="3">
         <v>71619608.079999998</v>
       </c>
-      <c r="D28" s="2">
-        <v>700445722.39999998</v>
-      </c>
-      <c r="E28" s="2">
+      <c r="D28" s="3">
+        <v>700445722.35000002</v>
+      </c>
+      <c r="E28" s="3">
         <v>2876000000</v>
       </c>
       <c r="F28" s="3">
@@ -1088,16 +1088,16 @@
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="2">
-        <v>14028846317</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1483600448</v>
-      </c>
-      <c r="D29" s="2">
-        <v>15512446765</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="B29" s="3">
+        <v>14028846316.700001</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1483600447.99</v>
+      </c>
+      <c r="D29" s="3">
+        <v>15512446764.690001</v>
+      </c>
+      <c r="E29" s="3">
         <v>41330450000</v>
       </c>
       <c r="F29" s="3">
@@ -1108,16 +1108,16 @@
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>151732064.19999999</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>171572177.09999999</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>323304241.30000001</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="3">
         <v>6796000000</v>
       </c>
       <c r="F30" s="3">
@@ -1128,36 +1128,36 @@
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="2">
-        <v>538449487.79999995</v>
+      <c r="B31" s="3">
+        <v>538449487.82000005</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
       </c>
-      <c r="D31" s="2">
-        <v>538449487.79999995</v>
+      <c r="D31" s="3">
+        <v>538449487.82000005</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
       <c r="F31" s="3">
-        <v>538449487.82000005</v>
+        <v>35317207630.279999</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>834738168.20000005</v>
       </c>
-      <c r="C32" s="2">
-        <v>238149795.80000001</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1072887964</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="C32" s="3">
+        <v>238149795.78999999</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1072887963.99</v>
+      </c>
+      <c r="E32" s="3">
         <v>2209000000</v>
       </c>
       <c r="F32" s="3">

--- a/Budget/data/budget_2025.xlsx
+++ b/Budget/data/budget_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FE5E27-D354-4590-9697-E76B5F0D4BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F199FD3-0F62-4B50-95B0-8584C4368B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{653CFB00-AA5A-438D-94B2-54F13C89823F}"/>
   </bookViews>
@@ -87,24 +87,12 @@
     <t>Judicial Service Commission</t>
   </si>
   <si>
-    <t>Anambra State Internal Revenue Service</t>
-  </si>
-  <si>
     <t>Ministry of Information</t>
   </si>
   <si>
     <t>Office of the Head of Service</t>
   </si>
   <si>
-    <t>Anambra State Investment Promotion &amp; Protection Agency</t>
-  </si>
-  <si>
-    <t>Christian Pilgrims Welfare Board</t>
-  </si>
-  <si>
-    <t>Muslim Pilgrims Welfare Board</t>
-  </si>
-  <si>
     <t>Ministry of Homeland Affairs</t>
   </si>
   <si>
@@ -136,12 +124,27 @@
   </si>
   <si>
     <t>Ministry of Lands</t>
+  </si>
+  <si>
+    <t>Office of the Auditor General</t>
+  </si>
+  <si>
+    <t>Civil Service Commision</t>
+  </si>
+  <si>
+    <t>Local Government Civil Service Commision</t>
+  </si>
+  <si>
+    <t>Awka Capital Territory Development Authority</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₦&quot;#,##0.00;[Red]\-&quot;₦&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,9 +154,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -192,15 +195,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,11 +520,10 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -544,624 +543,624 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>6699829526.5200005</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>31475545894.93</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>38175375421.459999</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>10664655500</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>48840030921.459999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>490472582.25</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>984312234.59000003</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1474784816.8399999</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>3019540000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>4494324816.8400002</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>23295299702.720001</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>20466144369.43</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>43761444072.160004</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>7664500000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>51425944072.160004</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>215899318.19999999</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>72949354.549999997</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>288848672.75</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>271562000000.10001</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>271850848672.85001</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
-        <v>283088351.72000003</v>
-      </c>
-      <c r="C6" s="3">
-        <v>28107274.530000001</v>
-      </c>
-      <c r="D6" s="3">
-        <v>312191149.89999998</v>
+      <c r="B6" s="2">
+        <v>130438464.84</v>
+      </c>
+      <c r="C6" s="2">
+        <v>139745476.19999999</v>
+      </c>
+      <c r="D6" s="2">
+        <v>270183941.04000002</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2849428941.04</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2579245000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2849428914.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>613367392.23000002</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>20339716.079999998</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>633707108.30999994</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>3125000000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>3758707108.3099999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>120066559.48</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>13384103.65</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>133450663.13</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>10411000000.049999</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>10544450663.18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>112311864</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>282383698.13</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>394695562.13</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>4569000000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>4963695562.1300001</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
-        <v>697308192.55999994</v>
+      <c r="B10" s="2">
+        <v>45107646.479999997</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>697308192.55999994</v>
+        <v>7513860000</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7558967646.4799995</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
+        <v>413000000</v>
+      </c>
+      <c r="F10" s="2">
         <v>7971967646.4799995</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>508275684.10000002</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>57531730.079999998</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>565807414.17999995</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>15336833333</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>15902640747.18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>22572200</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>19227600</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>41799800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>935000000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>976799800</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>1559128693.4400001</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>3245100260.8800001</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>4804228954.3199997</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>6058000000</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>10862228954.32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>70113487.5</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>19910052.690000001</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>90023540.189999998</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>185000000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>275023540.19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>5983750262.9399996</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>342004375.88</v>
       </c>
-      <c r="D15" s="3">
-        <v>6959461747.1199999</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D15" s="2">
+        <v>6325754638.8100004</v>
+      </c>
+      <c r="E15" s="2">
         <v>11299600000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>18259061747.119999</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
-        <v>565015287.39999998</v>
-      </c>
-      <c r="C16" s="3">
-        <v>109712371.73999999</v>
-      </c>
-      <c r="D16" s="3">
-        <v>674727659.13999999</v>
-      </c>
-      <c r="E16" s="3">
-        <v>699000000</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1373727659.1400001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>347591067.60000002</v>
+      </c>
+      <c r="C16" s="2">
+        <v>788911484.51999998</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1136502552.1199999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>5460318000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6596820552.1199999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
-        <v>347591067.60000002</v>
-      </c>
-      <c r="C17" s="3">
-        <v>788911484.51999998</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1136502552.1199999</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5460318000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6596820552.1199999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>1066410186.2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>295920722.08999997</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1362330908.29</v>
+      </c>
+      <c r="E17" s="2">
+        <v>866000000</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2228330908.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
-        <v>1066410186.2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>295920722.08999997</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1362330908.29</v>
-      </c>
-      <c r="E18" s="3">
-        <v>866000000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2228330908.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>135779993.05000001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>15107400</v>
+      </c>
+      <c r="D18" s="2">
+        <v>150887393.05000001</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2701500000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2852387393.0500002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
-        <v>221583990.03</v>
+      <c r="B19" s="2">
+        <v>160885117.59999999</v>
       </c>
       <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>221583990.03</v>
+        <v>37241657</v>
+      </c>
+      <c r="D19" s="2">
+        <v>198126774.59999999</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>221583990.03</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2764100000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2962226774.5999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
-        <v>7276500</v>
+      <c r="B20" s="2">
+        <v>138600177.31999999</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>7276500</v>
+        <v>30694000</v>
+      </c>
+      <c r="D20" s="2">
+        <v>169294177.31999999</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7276500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10609500000.02</v>
+      </c>
+      <c r="F20" s="2">
+        <v>10778794177.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
-        <v>7210350</v>
+      <c r="B21" s="2">
+        <v>280883462.60000002</v>
       </c>
       <c r="C21" s="2">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>7210350</v>
+        <v>29209950</v>
+      </c>
+      <c r="D21" s="2">
+        <v>310093412.60000002</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>7210350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>547000000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>857093412.60000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
-        <v>135779993.05000001</v>
-      </c>
-      <c r="C22" s="3">
-        <v>15107400</v>
-      </c>
-      <c r="D22" s="3">
-        <v>150887393.05000001</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2701500000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2852387393.0500002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>258086115.19999999</v>
+      </c>
+      <c r="C22" s="2">
+        <v>74436821.459999993</v>
+      </c>
+      <c r="D22" s="2">
+        <v>332522936.66000003</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4015000000.0999999</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4347522936.7600002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
-        <v>114446652.8</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9751322</v>
-      </c>
-      <c r="D23" s="3">
-        <v>124197974.8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2610600000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2962226774.5999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>576835303.79999995</v>
+      </c>
+      <c r="C23" s="2">
+        <v>43100895.200000003</v>
+      </c>
+      <c r="D23" s="2">
+        <v>619936199</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4109700000.0999999</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4729636199.1000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
-        <v>138600177.31999999</v>
-      </c>
-      <c r="C24" s="3">
-        <v>30694000</v>
-      </c>
-      <c r="D24" s="3">
-        <v>169294177.31999999</v>
-      </c>
-      <c r="E24" s="3">
-        <v>10609500000.02</v>
-      </c>
-      <c r="F24" s="3">
-        <v>10778794177.34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>628826114.26999998</v>
+      </c>
+      <c r="C24" s="2">
+        <v>71619608.079999998</v>
+      </c>
+      <c r="D24" s="2">
+        <v>700445722.35000002</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2876000000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3576445722.3499999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>280883462.60000002</v>
-      </c>
-      <c r="C25" s="3">
-        <v>29209950</v>
-      </c>
-      <c r="D25" s="3">
-        <v>310093412.60000002</v>
-      </c>
-      <c r="E25" s="3">
-        <v>547000000</v>
-      </c>
-      <c r="F25" s="3">
-        <v>857093412.60000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>14028846316.700001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1483600447.99</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15512446764.690001</v>
+      </c>
+      <c r="E25" s="2">
+        <v>41330450000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>56842896764.690002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>258086115.19999999</v>
-      </c>
-      <c r="C26" s="3">
-        <v>74436821.459999993</v>
-      </c>
-      <c r="D26" s="3">
-        <v>332522936.66000003</v>
-      </c>
-      <c r="E26" s="3">
-        <v>4015000000.0999999</v>
-      </c>
-      <c r="F26" s="3">
-        <v>4347522936.7600002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>151732064.19999999</v>
+      </c>
+      <c r="C26" s="2">
+        <v>171572177.09999999</v>
+      </c>
+      <c r="D26" s="2">
+        <v>323304241.30000001</v>
+      </c>
+      <c r="E26" s="2">
+        <v>6796000000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7119304241.3000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
-        <v>576835303.79999995</v>
-      </c>
-      <c r="C27" s="3">
-        <v>43100895.200000003</v>
-      </c>
-      <c r="D27" s="3">
-        <v>619936199</v>
-      </c>
-      <c r="E27" s="3">
-        <v>4109700000.0999999</v>
-      </c>
-      <c r="F27" s="3">
-        <v>4729636199.1000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>4484049575.6000004</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2899158054.6799998</v>
+      </c>
+      <c r="D27" s="2">
+        <v>7383207630.2799997</v>
+      </c>
+      <c r="E27" s="2">
+        <v>27934000000</v>
+      </c>
+      <c r="F27" s="2">
+        <v>35317207630.279999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
-        <v>628826114.26999998</v>
-      </c>
-      <c r="C28" s="3">
-        <v>71619608.079999998</v>
-      </c>
-      <c r="D28" s="3">
-        <v>700445722.35000002</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2876000000</v>
-      </c>
-      <c r="F28" s="3">
-        <v>3576445722.3499999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>834738168.20000005</v>
+      </c>
+      <c r="C28" s="2">
+        <v>238149795.78999999</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1072887963.99</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2209000000</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3281887963.9899998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3">
-        <v>14028846316.700001</v>
-      </c>
-      <c r="C29" s="3">
-        <v>1483600447.99</v>
-      </c>
-      <c r="D29" s="3">
-        <v>15512446764.690001</v>
-      </c>
-      <c r="E29" s="3">
-        <v>41330450000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>56842896764.690002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>306878351.60000002</v>
+      </c>
+      <c r="C29" s="2">
+        <v>18412310</v>
+      </c>
+      <c r="D29" s="2">
+        <v>325290661.60000002</v>
+      </c>
+      <c r="E29" s="2">
+        <v>204260004</v>
+      </c>
+      <c r="F29" s="2">
+        <v>529550665.60000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3">
-        <v>151732064.19999999</v>
-      </c>
-      <c r="C30" s="3">
-        <v>171572177.09999999</v>
-      </c>
-      <c r="D30" s="3">
-        <v>323304241.30000001</v>
-      </c>
-      <c r="E30" s="3">
-        <v>6796000000</v>
-      </c>
-      <c r="F30" s="3">
-        <v>7119304241.3000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>94969683.200000003</v>
+      </c>
+      <c r="C30" s="2">
+        <v>24258031</v>
+      </c>
+      <c r="D30" s="2">
+        <v>119227714.2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>70000000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>189227714.19999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="3">
-        <v>538449487.82000005</v>
+      <c r="B31" s="2">
+        <v>43769933.200000003</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
       </c>
-      <c r="D31" s="3">
-        <v>538449487.82000005</v>
+      <c r="D31" s="2">
+        <v>43769933.200000003</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="3">
-        <v>35317207630.279999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="2">
+        <v>43769933.200000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="3">
-        <v>834738168.20000005</v>
-      </c>
-      <c r="C32" s="3">
-        <v>238149795.78999999</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1072887963.99</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2209000000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3281887963.9899998</v>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>170080790</v>
+      </c>
+      <c r="D32" s="2">
+        <v>170080790</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>170080790</v>
       </c>
     </row>
   </sheetData>
